--- a/resources/templates/standard/J3100-07.xlsx
+++ b/resources/templates/standard/J3100-07.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>4M 변경점 관리 점검 C/SHEET</t>
   </si>
@@ -761,12 +764,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.95" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -788,7 +793,7 @@
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
@@ -826,20 +831,20 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
       <c r="Y2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
       <c r="AC2" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
       <c r="AF2" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
@@ -954,7 +959,7 @@
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -992,28 +997,28 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
       <c r="K7" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q7" s="12"/>
       <c r="R7" s="12"/>
@@ -1036,7 +1041,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -1074,7 +1079,7 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -1112,7 +1117,7 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -1150,7 +1155,7 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1188,7 +1193,7 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -1262,7 +1267,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1336,13 +1341,13 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
@@ -1356,7 +1361,7 @@
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
@@ -1372,7 +1377,7 @@
       <c r="AC16" s="12"/>
       <c r="AD16" s="12"/>
       <c r="AE16" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF16" s="12"/>
       <c r="AG16" s="12"/>
@@ -1380,13 +1385,13 @@
     </row>
     <row r="17" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
@@ -1420,7 +1425,7 @@
     </row>
     <row r="18" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -1458,7 +1463,7 @@
     </row>
     <row r="19" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -1496,7 +1501,7 @@
     </row>
     <row r="20" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="21"/>
@@ -1534,13 +1539,13 @@
     </row>
     <row r="21" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
       <c r="E21" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
@@ -1574,7 +1579,7 @@
     </row>
     <row r="22" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -1612,13 +1617,13 @@
     </row>
     <row r="23" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
@@ -1656,7 +1661,7 @@
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
@@ -1694,7 +1699,7 @@
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
@@ -1732,7 +1737,7 @@
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
       <c r="E26" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
@@ -1874,13 +1879,13 @@
     </row>
     <row r="30" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
       <c r="E30" s="25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30" s="25"/>
       <c r="G30" s="25"/>
@@ -1918,7 +1923,7 @@
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
       <c r="E31" s="25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" s="25"/>
       <c r="G31" s="25"/>
@@ -1956,7 +1961,7 @@
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" s="25"/>
       <c r="G32" s="25"/>
@@ -1994,7 +1999,7 @@
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
@@ -2032,7 +2037,7 @@
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
       <c r="E34" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F34" s="25"/>
       <c r="G34" s="25"/>
@@ -2138,13 +2143,13 @@
     </row>
     <row r="37" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
       <c r="E37" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37" s="25"/>
       <c r="G37" s="25"/>
@@ -2218,7 +2223,7 @@
       <c r="C39" s="15"/>
       <c r="D39" s="15"/>
       <c r="E39" s="25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F39" s="25"/>
       <c r="G39" s="25"/>
@@ -2396,13 +2401,13 @@
     </row>
     <row r="44" ht="17.1" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
       <c r="D44" s="15"/>
       <c r="E44" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F44" s="26"/>
       <c r="G44" s="26"/>
@@ -2476,7 +2481,7 @@
       <c r="C46" s="15"/>
       <c r="D46" s="15"/>
       <c r="E46" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F46" s="25"/>
       <c r="G46" s="25"/>
@@ -2514,7 +2519,7 @@
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
       <c r="E47" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F47" s="25"/>
       <c r="G47" s="25"/>
@@ -2552,7 +2557,7 @@
       <c r="C48" s="15"/>
       <c r="D48" s="15"/>
       <c r="E48" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F48" s="25"/>
       <c r="G48" s="25"/>
